--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="13770" windowHeight="6375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -89,43 +89,76 @@
     <t>注释</t>
   </si>
   <si>
-    <t>test.quality_type</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>黑</t>
-  </si>
-  <si>
-    <t>黑色的</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最差品质</t>
+    <t>sex_type</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>red_dot_type</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>角色功能类</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>物品功能类</t>
+  </si>
+  <si>
+    <t>activity</t>
+  </si>
+  <si>
+    <t>活动功能类</t>
+  </si>
+  <si>
+    <t>develop</t>
+  </si>
+  <si>
+    <t>养成功能类</t>
+  </si>
+  <si>
+    <t>mail</t>
+  </si>
+  <si>
+    <t>邮件功能类</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>任务功能类</t>
+  </si>
+  <si>
+    <t>attribute</t>
+  </si>
+  <si>
+    <t>属性功能类</t>
+  </si>
+  <si>
+    <t>instance</t>
+  </si>
+  <si>
+    <t>副本功能类</t>
   </si>
 </sst>
 </file>
@@ -1100,8 +1133,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
     <col min="3" max="4" width="31.75" customWidth="1"/>
@@ -1219,52 +1252,173 @@
         <v>22</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
         <v>28</v>
       </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="I9" t="s">
         <v>29</v>
       </c>
+      <c r="J9">
+        <v>10000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="H7" t="s">
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I10" t="s">
         <v>31</v>
       </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="J10">
+        <v>20000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" t="s">
         <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11">
+        <v>30000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <v>40000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13">
+        <v>50000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14">
+        <v>60000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15">
+        <v>70000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16">
+        <v>80000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="13770" windowHeight="6375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -159,6 +159,42 @@
   </si>
   <si>
     <t>副本功能类</t>
+  </si>
+  <si>
+    <t>red_dot_status_type</t>
+  </si>
+  <si>
+    <t>exist</t>
+  </si>
+  <si>
+    <t>存在</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>和</t>
+  </si>
+  <si>
+    <t>item_type</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>定制</t>
+  </si>
+  <si>
+    <t>consumable</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>装备</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1421,6 +1457,99 @@
         <v>43</v>
       </c>
     </row>
+    <row r="18" spans="2:11">
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="H19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="H22" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="H24" t="s">
+        <v>54</v>
+      </c>
+      <c r="I24" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -195,6 +195,33 @@
   </si>
   <si>
     <t>装备</t>
+  </si>
+  <si>
+    <t>develop_system_type</t>
+  </si>
+  <si>
+    <t>develop_sub_type</t>
+  </si>
+  <si>
+    <t>develop_reset_type</t>
+  </si>
+  <si>
+    <t>non_resettable</t>
+  </si>
+  <si>
+    <t>不可重置</t>
+  </si>
+  <si>
+    <t>refund</t>
+  </si>
+  <si>
+    <t>返还</t>
+  </si>
+  <si>
+    <t>partial_refund</t>
+  </si>
+  <si>
+    <t>部分返还</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1550,6 +1577,103 @@
         <v>3</v>
       </c>
     </row>
+    <row r="26" spans="2:11">
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" t="s">
+        <v>60</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="H31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="H32" t="s">
+        <v>63</v>
+      </c>
+      <c r="I32" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -195,6 +195,24 @@
   </si>
   <si>
     <t>装备</t>
+  </si>
+  <si>
+    <t>Avatar</t>
+  </si>
+  <si>
+    <t>头像</t>
+  </si>
+  <si>
+    <t>Frame</t>
+  </si>
+  <si>
+    <t>头像框</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>称号</t>
   </si>
   <si>
     <t>develop_system_type</t>
@@ -1196,7 +1214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1577,101 +1595,134 @@
         <v>3</v>
       </c>
     </row>
+    <row r="25" spans="2:11">
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+    </row>
     <row r="26" spans="2:11">
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" t="b">
+      <c r="H26" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="H27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="b">
         <v>0</v>
       </c>
-      <c r="E26" t="b">
+      <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H29" t="s">
         <v>21</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I29" t="s">
         <v>22</v>
       </c>
-      <c r="J26">
+      <c r="J29">
         <v>0</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
-      <c r="B28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" t="b">
+    <row r="31" spans="2:11">
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="b">
         <v>0</v>
       </c>
-      <c r="E28" t="b">
+      <c r="E31" t="b">
         <v>1</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H31" t="s">
         <v>21</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I31" t="s">
         <v>22</v>
       </c>
-      <c r="J28">
+      <c r="J31">
         <v>0</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
-      <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" t="b">
+    <row r="33" spans="2:11">
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="b">
         <v>0</v>
       </c>
-      <c r="E30" t="b">
+      <c r="E33" t="b">
         <v>1</v>
       </c>
-      <c r="H30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I30" t="s">
-        <v>60</v>
-      </c>
-      <c r="J30">
+      <c r="H33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" t="s">
+        <v>66</v>
+      </c>
+      <c r="J33">
         <v>0</v>
       </c>
-      <c r="K30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="H31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" t="s">
-        <v>62</v>
-      </c>
-      <c r="J31">
+      <c r="K33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="H34" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" t="s">
+        <v>68</v>
+      </c>
+      <c r="J34">
         <v>1</v>
       </c>
-      <c r="K31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="H32" t="s">
-        <v>63</v>
-      </c>
-      <c r="I32" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32">
+      <c r="K34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="H35" t="s">
+        <v>69</v>
+      </c>
+      <c r="I35" t="s">
+        <v>70</v>
+      </c>
+      <c r="J35">
         <v>2</v>
       </c>
-      <c r="K32" t="s">
-        <v>64</v>
+      <c r="K35" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>称号</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>英雄</t>
   </si>
   <si>
     <t>develop_system_type</t>
@@ -1214,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1572,6 +1578,9 @@
       <c r="J22">
         <v>1</v>
       </c>
+      <c r="K22" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="23" spans="2:11">
       <c r="H23" t="s">
@@ -1583,6 +1592,9 @@
       <c r="J23">
         <v>2</v>
       </c>
+      <c r="K23" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="24" spans="2:11">
       <c r="H24" t="s">
@@ -1594,6 +1606,9 @@
       <c r="J24">
         <v>3</v>
       </c>
+      <c r="K24" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" spans="2:11">
       <c r="H25" t="s">
@@ -1605,6 +1620,9 @@
       <c r="J25">
         <v>4</v>
       </c>
+      <c r="K25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="26" spans="2:11">
       <c r="H26" t="s">
@@ -1616,6 +1634,9 @@
       <c r="J26">
         <v>5</v>
       </c>
+      <c r="K26" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="27" spans="2:11">
       <c r="H27" t="s">
@@ -1627,77 +1648,80 @@
       <c r="J27">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" t="s">
+      <c r="K27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="H28" t="s">
         <v>62</v>
       </c>
-      <c r="C29" t="b">
+      <c r="I28" t="s">
+        <v>63</v>
+      </c>
+      <c r="J28">
+        <v>7</v>
+      </c>
+      <c r="K28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="b">
         <v>0</v>
       </c>
-      <c r="E29" t="b">
+      <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H30" t="s">
         <v>21</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I30" t="s">
         <v>22</v>
       </c>
-      <c r="J29">
+      <c r="J30">
         <v>0</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="b">
+    <row r="32" spans="2:11">
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="b">
         <v>0</v>
       </c>
-      <c r="E31" t="b">
+      <c r="E32" t="b">
         <v>1</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H32" t="s">
         <v>21</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I32" t="s">
         <v>22</v>
       </c>
-      <c r="J31">
+      <c r="J32">
         <v>0</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K32" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
-      <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" t="b">
+    <row r="34" spans="2:11">
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="b">
         <v>0</v>
       </c>
-      <c r="E33" t="b">
+      <c r="E34" t="b">
         <v>1</v>
       </c>
-      <c r="H33" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33" t="s">
-        <v>66</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
       <c r="H34" t="s">
         <v>67</v>
       </c>
@@ -1705,7 +1729,7 @@
         <v>68</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
@@ -1719,10 +1743,24 @@
         <v>70</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="H36" t="s">
+        <v>71</v>
+      </c>
+      <c r="I36" t="s">
+        <v>72</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -197,28 +197,31 @@
     <t>装备</t>
   </si>
   <si>
-    <t>Avatar</t>
+    <t>avatar</t>
   </si>
   <si>
     <t>头像</t>
   </si>
   <si>
-    <t>Frame</t>
+    <t>frame</t>
   </si>
   <si>
     <t>头像框</t>
   </si>
   <si>
-    <t>Title</t>
+    <t>title</t>
   </si>
   <si>
     <t>称号</t>
   </si>
   <si>
-    <t>Hero</t>
+    <t>hero</t>
   </si>
   <si>
     <t>英雄</t>
+  </si>
+  <si>
+    <t>item_selected_child_type</t>
   </si>
   <si>
     <t>develop_system_type</t>
@@ -1220,7 +1223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1666,7 +1669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
+    <row r="30" customFormat="1" spans="2:11">
       <c r="B30" t="s">
         <v>64</v>
       </c>
@@ -1723,44 +1726,67 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="H35" t="s">
+      <c r="I36" t="s">
         <v>69</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="H37" t="s">
         <v>70</v>
       </c>
-      <c r="J35">
+      <c r="I37" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37">
         <v>1</v>
       </c>
-      <c r="K35" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="H36" t="s">
+      <c r="K37" t="s">
         <v>71</v>
       </c>
-      <c r="I36" t="s">
+    </row>
+    <row r="38" spans="2:11">
+      <c r="H38" t="s">
         <v>72</v>
       </c>
-      <c r="J36">
+      <c r="I38" t="s">
+        <v>73</v>
+      </c>
+      <c r="J38">
         <v>2</v>
       </c>
-      <c r="K36" t="s">
-        <v>72</v>
+      <c r="K38" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>develop_sub_type</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>升级</t>
   </si>
   <si>
     <t>develop_reset_type</t>
@@ -1223,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1715,78 +1721,106 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
-      <c r="B34" t="s">
+    <row r="33" spans="2:11">
+      <c r="H33" t="s">
+        <v>62</v>
+      </c>
+      <c r="I33" t="s">
+        <v>63</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" t="s">
         <v>66</v>
       </c>
-      <c r="C34" t="b">
+      <c r="C35" t="b">
         <v>0</v>
       </c>
-      <c r="E34" t="b">
+      <c r="E35" t="b">
         <v>1</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H35" t="s">
         <v>21</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I35" t="s">
         <v>22</v>
       </c>
-      <c r="J34">
+      <c r="J35">
         <v>0</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="2:11">
-      <c r="B36" t="s">
+      <c r="H36" t="s">
         <v>67</v>
       </c>
-      <c r="C36" t="b">
+      <c r="I36" t="s">
+        <v>68</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="b">
         <v>0</v>
       </c>
-      <c r="E36" t="b">
+      <c r="E38" t="b">
         <v>1</v>
       </c>
-      <c r="H36" t="s">
-        <v>68</v>
-      </c>
-      <c r="I36" t="s">
-        <v>69</v>
-      </c>
-      <c r="J36">
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38">
         <v>0</v>
       </c>
-      <c r="K36" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="H37" t="s">
-        <v>70</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="K38" t="s">
         <v>71</v>
       </c>
-      <c r="J37">
+    </row>
+    <row r="39" spans="2:11">
+      <c r="H39" t="s">
+        <v>72</v>
+      </c>
+      <c r="I39" t="s">
+        <v>73</v>
+      </c>
+      <c r="J39">
         <v>1</v>
       </c>
-      <c r="K37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="H38" t="s">
-        <v>72</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="K39" t="s">
         <v>73</v>
       </c>
-      <c r="J38">
+    </row>
+    <row r="40" spans="2:11">
+      <c r="H40" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s">
+        <v>75</v>
+      </c>
+      <c r="J40">
         <v>2</v>
       </c>
-      <c r="K38" t="s">
-        <v>73</v>
+      <c r="K40" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -255,6 +255,18 @@
   </si>
   <si>
     <t>部分返还</t>
+  </si>
+  <si>
+    <t>task_event_type</t>
+  </si>
+  <si>
+    <t>kill_monster</t>
+  </si>
+  <si>
+    <t>击杀怪物</t>
+  </si>
+  <si>
+    <t>upgrade_level</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1241,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1823,6 +1835,57 @@
         <v>75</v>
       </c>
     </row>
+    <row r="42" spans="2:11">
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="H43" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s">
+        <v>78</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="H44" t="s">
+        <v>79</v>
+      </c>
+      <c r="I44" t="s">
+        <v>68</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>upgrade_level</t>
+  </si>
+  <si>
+    <t>task_component_type</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>主线</t>
+  </si>
+  <si>
+    <t>daily</t>
+  </si>
+  <si>
+    <t>每日</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1259,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1886,6 +1904,52 @@
         <v>68</v>
       </c>
     </row>
+    <row r="46" customFormat="1" spans="2:11">
+      <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>81</v>
+      </c>
+      <c r="I46" t="s">
+        <v>82</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="2:11">
+      <c r="H47" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" t="s">
+        <v>84</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="2:11">
+      <c r="H48" t="s">
+        <v>85</v>
+      </c>
+      <c r="I48"/>
+      <c r="J48">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="107">
   <si>
     <t>##var</t>
   </si>
@@ -285,6 +285,69 @@
   </si>
   <si>
     <t>max</t>
+  </si>
+  <si>
+    <t>quality_type</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>uncommon</t>
+  </si>
+  <si>
+    <t>优秀</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>rare</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>epic</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>legendary</t>
+  </si>
+  <si>
+    <t>传说</t>
+  </si>
+  <si>
+    <t>橙</t>
+  </si>
+  <si>
+    <t>mythic</t>
+  </si>
+  <si>
+    <t>神话</t>
+  </si>
+  <si>
+    <t>红</t>
+  </si>
+  <si>
+    <t>avatar_type</t>
+  </si>
+  <si>
+    <t>attribute_type</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1322,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1950,6 +2013,173 @@
         <v>2</v>
       </c>
     </row>
+    <row r="50" spans="2:11">
+      <c r="B50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="H51" t="s">
+        <v>87</v>
+      </c>
+      <c r="I51" t="s">
+        <v>88</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="H52" t="s">
+        <v>90</v>
+      </c>
+      <c r="I52" t="s">
+        <v>91</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="H53" t="s">
+        <v>93</v>
+      </c>
+      <c r="I53" t="s">
+        <v>94</v>
+      </c>
+      <c r="J53">
+        <v>3</v>
+      </c>
+      <c r="K53" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="H54" t="s">
+        <v>96</v>
+      </c>
+      <c r="I54" t="s">
+        <v>97</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
+      <c r="K54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
+      <c r="H55" t="s">
+        <v>99</v>
+      </c>
+      <c r="I55" t="s">
+        <v>100</v>
+      </c>
+      <c r="J55">
+        <v>5</v>
+      </c>
+      <c r="K55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
+      <c r="H56" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" t="s">
+        <v>103</v>
+      </c>
+      <c r="J56">
+        <v>6</v>
+      </c>
+      <c r="K56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" t="s">
+        <v>105</v>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="H59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I59" t="s">
+        <v>88</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="15150" windowHeight="7005"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="109">
   <si>
     <t>##var</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>upgrade_level</t>
+  </si>
+  <si>
+    <t>hold_item</t>
+  </si>
+  <si>
+    <t>拥有物品</t>
   </si>
   <si>
     <t>task_component_type</t>
@@ -1322,7 +1328,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1967,30 +1973,30 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="2:11">
-      <c r="B46" t="s">
+    <row r="45" spans="2:11">
+      <c r="H45" t="s">
         <v>80</v>
       </c>
-      <c r="C46" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="I45" t="s">
         <v>81</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J45">
+        <v>3</v>
+      </c>
+      <c r="K45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="2:11">
+      <c r="B47" t="s">
         <v>82</v>
       </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="2:11">
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
       <c r="H47" t="s">
         <v>83</v>
       </c>
@@ -1998,7 +2004,7 @@
         <v>84</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="s">
         <v>84</v>
@@ -2008,175 +2014,203 @@
       <c r="H48" t="s">
         <v>85</v>
       </c>
-      <c r="I48"/>
+      <c r="I48" t="s">
+        <v>86</v>
+      </c>
       <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="2:11">
+      <c r="H49" t="s">
+        <v>56</v>
+      </c>
+      <c r="I49" t="s">
+        <v>57</v>
+      </c>
+      <c r="J49">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
+      <c r="K49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="2:11">
       <c r="H50" t="s">
+        <v>87</v>
+      </c>
+      <c r="I50"/>
+      <c r="J50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
         <v>21</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I52" t="s">
         <v>22</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="H51" t="s">
-        <v>87</v>
-      </c>
-      <c r="I51" t="s">
-        <v>88</v>
-      </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="H52" t="s">
-        <v>90</v>
-      </c>
-      <c r="I52" t="s">
-        <v>91</v>
-      </c>
-      <c r="J52">
-        <v>2</v>
-      </c>
-      <c r="K52" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="53" spans="2:11">
       <c r="H53" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="2:11">
       <c r="H54" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I54" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="2:11">
       <c r="H55" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I55" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="2:11">
       <c r="H56" t="s">
+        <v>98</v>
+      </c>
+      <c r="I56" t="s">
+        <v>99</v>
+      </c>
+      <c r="J56">
+        <v>4</v>
+      </c>
+      <c r="K56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="H57" t="s">
+        <v>101</v>
+      </c>
+      <c r="I57" t="s">
         <v>102</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J57">
+        <v>5</v>
+      </c>
+      <c r="K57" t="s">
         <v>103</v>
       </c>
-      <c r="J56">
+    </row>
+    <row r="58" spans="2:11">
+      <c r="H58" t="s">
+        <v>104</v>
+      </c>
+      <c r="I58" t="s">
+        <v>105</v>
+      </c>
+      <c r="J58">
         <v>6</v>
       </c>
-      <c r="K56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" t="s">
-        <v>105</v>
-      </c>
-      <c r="C58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="K58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="B60" t="s">
+        <v>107</v>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
         <v>21</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I60" t="s">
         <v>22</v>
       </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58" t="s">
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="2:11">
-      <c r="H59" t="s">
-        <v>87</v>
-      </c>
-      <c r="I59" t="s">
-        <v>88</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59" t="s">
-        <v>88</v>
-      </c>
-    </row>
     <row r="61" spans="2:11">
-      <c r="B61" t="s">
-        <v>106</v>
-      </c>
-      <c r="C61" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
       <c r="H61" t="s">
+        <v>89</v>
+      </c>
+      <c r="I61" t="s">
+        <v>90</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
         <v>21</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I63" t="s">
         <v>22</v>
       </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61" t="s">
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15150" windowHeight="7005"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -353,7 +353,28 @@
     <t>avatar_type</t>
   </si>
   <si>
+    <t>emperor</t>
+  </si>
+  <si>
+    <t>帝王</t>
+  </si>
+  <si>
+    <t>harem</t>
+  </si>
+  <si>
+    <t>后宫</t>
+  </si>
+  <si>
+    <t>minister</t>
+  </si>
+  <si>
+    <t>名臣</t>
+  </si>
+  <si>
     <t>attribute_type</t>
+  </si>
+  <si>
+    <t>hero_type</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -2191,27 +2212,148 @@
         <v>90</v>
       </c>
     </row>
+    <row r="62" spans="2:11">
+      <c r="H62" t="s">
+        <v>108</v>
+      </c>
+      <c r="I62" t="s">
+        <v>109</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="63" spans="2:11">
-      <c r="B63" t="s">
+      <c r="H63" t="s">
+        <v>110</v>
+      </c>
+      <c r="I63" t="s">
+        <v>111</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="H64" t="s">
+        <v>112</v>
+      </c>
+      <c r="I64" t="s">
+        <v>113</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="2:11">
+      <c r="B68" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="2:11">
+      <c r="H69" t="s">
+        <v>89</v>
+      </c>
+      <c r="I69" t="s">
+        <v>90</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="H70" t="s">
         <v>108</v>
       </c>
-      <c r="C63" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" t="s">
-        <v>21</v>
-      </c>
-      <c r="I63" t="s">
-        <v>22</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63" t="s">
-        <v>22</v>
+      <c r="I70" t="s">
+        <v>109</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="H71" t="s">
+        <v>110</v>
+      </c>
+      <c r="I71" t="s">
+        <v>111</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="H72" t="s">
+        <v>112</v>
+      </c>
+      <c r="I72" t="s">
+        <v>113</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="117">
   <si>
     <t>##var</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>名臣</t>
+  </si>
+  <si>
+    <t>frame_type</t>
   </si>
   <si>
     <t>attribute_type</t>
@@ -1349,7 +1352,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -2061,298 +2064,350 @@
     </row>
     <row r="50" customFormat="1" spans="2:11">
       <c r="H50" t="s">
-        <v>87</v>
-      </c>
-      <c r="I50"/>
+        <v>58</v>
+      </c>
+      <c r="I50" t="s">
+        <v>59</v>
+      </c>
       <c r="J50">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" t="s">
+      <c r="K50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="2:11">
+      <c r="H51" t="s">
+        <v>87</v>
+      </c>
+      <c r="I51"/>
+      <c r="J51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" t="s">
         <v>88</v>
       </c>
-      <c r="C52" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
         <v>21</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I53" t="s">
         <v>22</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="H53" t="s">
-        <v>89</v>
-      </c>
-      <c r="I53" t="s">
-        <v>90</v>
-      </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="54" spans="2:11">
       <c r="H54" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="2:11">
       <c r="H55" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="2:11">
       <c r="H56" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I56" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="H57" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I57" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="2:11">
       <c r="H58" t="s">
+        <v>101</v>
+      </c>
+      <c r="I58" t="s">
+        <v>102</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
+      <c r="K58" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="H59" t="s">
         <v>104</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I59" t="s">
         <v>105</v>
       </c>
-      <c r="J58">
+      <c r="J59">
         <v>6</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K59" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="2:11">
-      <c r="B60" t="s">
+    <row r="61" spans="2:11">
+      <c r="B61" t="s">
         <v>107</v>
       </c>
-      <c r="C60" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="C61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
         <v>21</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I61" t="s">
         <v>22</v>
       </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60" t="s">
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="H61" t="s">
-        <v>89</v>
-      </c>
-      <c r="I61" t="s">
-        <v>90</v>
-      </c>
-      <c r="J61">
-        <v>1</v>
-      </c>
-      <c r="K61" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="H62" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I62" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="2:11">
       <c r="H63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I63" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="2:11">
       <c r="H64" t="s">
+        <v>110</v>
+      </c>
+      <c r="I64" t="s">
+        <v>111</v>
+      </c>
+      <c r="J64">
+        <v>3</v>
+      </c>
+      <c r="K64" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="H65" t="s">
         <v>112</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I65" t="s">
         <v>113</v>
       </c>
-      <c r="J64">
+      <c r="J65">
         <v>4</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K65" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="66" spans="2:11">
-      <c r="B66" t="s">
+    <row r="66" customFormat="1"/>
+    <row r="67" customFormat="1" spans="2:11">
+      <c r="B67" t="s">
         <v>114</v>
       </c>
-      <c r="C66" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="C67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
         <v>21</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I67" t="s">
         <v>22</v>
       </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66" t="s">
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="2:11">
-      <c r="B68" t="s">
+      <c r="H68" t="s">
+        <v>89</v>
+      </c>
+      <c r="I68" t="s">
+        <v>90</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" t="s">
         <v>115</v>
       </c>
-      <c r="C68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E68" t="b">
-        <v>1</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
         <v>21</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I70" t="s">
         <v>22</v>
       </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68" t="s">
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="69" customFormat="1" spans="2:11">
-      <c r="H69" t="s">
+    <row r="72" customFormat="1" spans="2:11">
+      <c r="B72" t="s">
+        <v>116</v>
+      </c>
+      <c r="C72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="2:11">
+      <c r="H73" t="s">
         <v>89</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I73" t="s">
         <v>90</v>
       </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="K69" t="s">
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="2:11">
-      <c r="H70" t="s">
+    <row r="74" spans="2:11">
+      <c r="H74" t="s">
         <v>108</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I74" t="s">
         <v>109</v>
       </c>
-      <c r="J70">
+      <c r="J74">
         <v>2</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K74" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="71" spans="2:11">
-      <c r="H71" t="s">
+    <row r="75" spans="2:11">
+      <c r="H75" t="s">
         <v>110</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I75" t="s">
         <v>111</v>
       </c>
-      <c r="J71">
+      <c r="J75">
         <v>3</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K75" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="2:11">
-      <c r="H72" t="s">
+    <row r="76" spans="2:11">
+      <c r="H76" t="s">
         <v>112</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I76" t="s">
         <v>113</v>
       </c>
-      <c r="J72">
+      <c r="J76">
         <v>4</v>
       </c>
-      <c r="K72" t="s">
+      <c r="K76" t="s">
         <v>113</v>
       </c>
     </row>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -221,10 +221,22 @@
     <t>英雄</t>
   </si>
   <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
     <t>item_selected_child_type</t>
   </si>
   <si>
     <t>develop_system_type</t>
+  </si>
+  <si>
+    <t>角色</t>
+  </si>
+  <si>
+    <t>vip</t>
   </si>
   <si>
     <t>develop_sub_type</t>
@@ -1352,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1798,106 +1810,109 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="2:11">
-      <c r="B30" t="s">
+    <row r="29" spans="2:11">
+      <c r="H29" t="s">
         <v>64</v>
       </c>
-      <c r="C30" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="I29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="K29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="2:11">
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
         <v>21</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I31" t="s">
         <v>22</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="s">
+    <row r="33" spans="2:11">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
         <v>21</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I33" t="s">
         <v>22</v>
       </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
-      <c r="H33" t="s">
-        <v>62</v>
-      </c>
-      <c r="I33" t="s">
-        <v>63</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33" t="s">
-        <v>63</v>
+    <row r="34" spans="2:11">
+      <c r="H34" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" t="s">
+        <v>68</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:11">
-      <c r="B35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
       <c r="H35" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" t="s">
-        <v>22</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I35"/>
       <c r="J35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="B38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
@@ -1906,412 +1921,411 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="H39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39" t="s">
         <v>72</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" t="s">
         <v>73</v>
       </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="H40" t="s">
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
         <v>74</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I41" t="s">
         <v>75</v>
       </c>
-      <c r="J40">
-        <v>2</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="42" spans="2:11">
-      <c r="B42" t="s">
+      <c r="H42" t="s">
         <v>76</v>
       </c>
-      <c r="C42" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="s">
-        <v>21</v>
-      </c>
       <c r="I42" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="2:11">
       <c r="H43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="H44" t="s">
         <v>79</v>
       </c>
-      <c r="I44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-      <c r="K44" t="s">
-        <v>68</v>
-      </c>
     </row>
     <row r="45" spans="2:11">
+      <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
       <c r="H45" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="H46" t="s">
         <v>81</v>
       </c>
-      <c r="J45">
-        <v>3</v>
-      </c>
-      <c r="K45" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="2:11">
-      <c r="B47" t="s">
+      <c r="I46" t="s">
         <v>82</v>
       </c>
-      <c r="C47" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
       <c r="H47" t="s">
         <v>83</v>
       </c>
       <c r="I47" t="s">
+        <v>72</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="H48" t="s">
         <v>84</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="2:11">
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>85</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48">
+        <v>3</v>
+      </c>
+      <c r="K48" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="2:11">
+      <c r="B50" t="s">
         <v>86</v>
       </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-      <c r="K48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="2:11">
-      <c r="H49" t="s">
-        <v>56</v>
-      </c>
-      <c r="I49" t="s">
-        <v>57</v>
-      </c>
-      <c r="J49">
-        <v>2</v>
-      </c>
-      <c r="K49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="2:11">
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="I50" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="2:11">
       <c r="H51" t="s">
-        <v>87</v>
-      </c>
-      <c r="I51"/>
+        <v>89</v>
+      </c>
+      <c r="I51" t="s">
+        <v>90</v>
+      </c>
       <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="2:11">
+      <c r="H52" t="s">
+        <v>56</v>
+      </c>
+      <c r="I52" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="2:11">
+      <c r="H53" t="s">
+        <v>58</v>
+      </c>
+      <c r="I53" t="s">
+        <v>59</v>
+      </c>
+      <c r="J53">
+        <v>3</v>
+      </c>
+      <c r="K53" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="2:11">
+      <c r="H54" t="s">
+        <v>91</v>
+      </c>
+      <c r="I54"/>
+      <c r="J54">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="2:11">
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
+    <row r="56" spans="2:11">
+      <c r="B56" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
         <v>21</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I56" t="s">
         <v>22</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53" t="s">
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="H54" t="s">
-        <v>89</v>
-      </c>
-      <c r="I54" t="s">
-        <v>90</v>
-      </c>
-      <c r="J54">
-        <v>1</v>
-      </c>
-      <c r="K54" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="H55" t="s">
-        <v>92</v>
-      </c>
-      <c r="I55" t="s">
-        <v>93</v>
-      </c>
-      <c r="J55">
-        <v>2</v>
-      </c>
-      <c r="K55" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="H56" t="s">
-        <v>95</v>
-      </c>
-      <c r="I56" t="s">
-        <v>96</v>
-      </c>
-      <c r="J56">
-        <v>3</v>
-      </c>
-      <c r="K56" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="H57" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I57" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="2:11">
       <c r="H58" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I58" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="2:11">
       <c r="H59" t="s">
+        <v>99</v>
+      </c>
+      <c r="I59" t="s">
+        <v>100</v>
+      </c>
+      <c r="J59">
+        <v>3</v>
+      </c>
+      <c r="K59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="H60" t="s">
+        <v>102</v>
+      </c>
+      <c r="I60" t="s">
+        <v>103</v>
+      </c>
+      <c r="J60">
+        <v>4</v>
+      </c>
+      <c r="K60" t="s">
         <v>104</v>
       </c>
-      <c r="I59" t="s">
+    </row>
+    <row r="61" spans="2:11">
+      <c r="H61" t="s">
         <v>105</v>
       </c>
-      <c r="J59">
-        <v>6</v>
-      </c>
-      <c r="K59" t="s">
+      <c r="I61" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" t="s">
+      <c r="J61">
+        <v>5</v>
+      </c>
+      <c r="K61" t="s">
         <v>107</v>
-      </c>
-      <c r="C61" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="H62" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="I62" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K62" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="H63" t="s">
-        <v>108</v>
-      </c>
-      <c r="I63" t="s">
-        <v>109</v>
-      </c>
-      <c r="J63">
-        <v>2</v>
-      </c>
-      <c r="K63" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="2:11">
+      <c r="B64" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
       <c r="H64" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="2:11">
       <c r="H65" t="s">
+        <v>93</v>
+      </c>
+      <c r="I65" t="s">
+        <v>94</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="H66" t="s">
         <v>112</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I66" t="s">
         <v>113</v>
       </c>
-      <c r="J65">
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="H67" t="s">
+        <v>114</v>
+      </c>
+      <c r="I67" t="s">
+        <v>115</v>
+      </c>
+      <c r="J67">
+        <v>3</v>
+      </c>
+      <c r="K67" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="H68" t="s">
+        <v>116</v>
+      </c>
+      <c r="I68" t="s">
+        <v>117</v>
+      </c>
+      <c r="J68">
         <v>4</v>
       </c>
-      <c r="K65" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1" spans="2:11">
-      <c r="B67" t="s">
-        <v>114</v>
-      </c>
-      <c r="C67" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67" t="s">
-        <v>22</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" spans="2:11">
-      <c r="H68" t="s">
-        <v>89</v>
-      </c>
-      <c r="I68" t="s">
-        <v>90</v>
-      </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
       <c r="K68" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="2:11">
       <c r="B70" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C70" t="b">
         <v>0</v>
@@ -2332,83 +2346,120 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" customFormat="1" spans="2:11">
-      <c r="B72" t="s">
+    <row r="71" customFormat="1" spans="2:11">
+      <c r="H71" t="s">
+        <v>93</v>
+      </c>
+      <c r="I71" t="s">
+        <v>94</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="2:11">
+      <c r="B75" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="2:11">
+      <c r="H76" t="s">
+        <v>93</v>
+      </c>
+      <c r="I76" t="s">
+        <v>94</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="H77" t="s">
+        <v>112</v>
+      </c>
+      <c r="I77" t="s">
+        <v>113</v>
+      </c>
+      <c r="J77">
+        <v>2</v>
+      </c>
+      <c r="K77" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="H78" t="s">
+        <v>114</v>
+      </c>
+      <c r="I78" t="s">
+        <v>115</v>
+      </c>
+      <c r="J78">
+        <v>3</v>
+      </c>
+      <c r="K78" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="H79" t="s">
         <v>116</v>
       </c>
-      <c r="C72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" t="s">
-        <v>22</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" customFormat="1" spans="2:11">
-      <c r="H73" t="s">
-        <v>89</v>
-      </c>
-      <c r="I73" t="s">
-        <v>90</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="K73" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="H74" t="s">
-        <v>108</v>
-      </c>
-      <c r="I74" t="s">
-        <v>109</v>
-      </c>
-      <c r="J74">
-        <v>2</v>
-      </c>
-      <c r="K74" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="H75" t="s">
-        <v>110</v>
-      </c>
-      <c r="I75" t="s">
-        <v>111</v>
-      </c>
-      <c r="J75">
-        <v>3</v>
-      </c>
-      <c r="K75" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="H76" t="s">
-        <v>112</v>
-      </c>
-      <c r="I76" t="s">
-        <v>113</v>
-      </c>
-      <c r="J76">
+      <c r="I79" t="s">
+        <v>117</v>
+      </c>
+      <c r="J79">
         <v>4</v>
       </c>
-      <c r="K76" t="s">
-        <v>113</v>
+      <c r="K79" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -390,6 +390,51 @@
   </si>
   <si>
     <t>hero_type</t>
+  </si>
+  <si>
+    <t>currency_type</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>黄金</t>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>白银</t>
+  </si>
+  <si>
+    <t>copper_coin</t>
+  </si>
+  <si>
+    <t>铜钱</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>粮食</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>石头</t>
+  </si>
+  <si>
+    <t>iron_ore</t>
+  </si>
+  <si>
+    <t>铁矿</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1409,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1888,7 +1933,6 @@
       <c r="H35" t="s">
         <v>69</v>
       </c>
-      <c r="I35"/>
       <c r="J35">
         <v>2</v>
       </c>
@@ -2460,6 +2504,127 @@
       </c>
       <c r="K79" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="2:11">
+      <c r="B81" t="s">
+        <v>121</v>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="H82" t="s">
+        <v>122</v>
+      </c>
+      <c r="I82" t="s">
+        <v>123</v>
+      </c>
+      <c r="J82">
+        <v>1001001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="H83" t="s">
+        <v>124</v>
+      </c>
+      <c r="I83" t="s">
+        <v>125</v>
+      </c>
+      <c r="J83">
+        <v>1001002</v>
+      </c>
+      <c r="K83" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="H84" t="s">
+        <v>126</v>
+      </c>
+      <c r="I84" t="s">
+        <v>127</v>
+      </c>
+      <c r="J84">
+        <v>1001003</v>
+      </c>
+      <c r="K84" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="H85" t="s">
+        <v>128</v>
+      </c>
+      <c r="I85" t="s">
+        <v>129</v>
+      </c>
+      <c r="J85">
+        <v>1021001</v>
+      </c>
+      <c r="K85" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="H86" t="s">
+        <v>130</v>
+      </c>
+      <c r="I86" t="s">
+        <v>131</v>
+      </c>
+      <c r="J86">
+        <v>1021002</v>
+      </c>
+      <c r="K86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="H87" t="s">
+        <v>132</v>
+      </c>
+      <c r="I87" t="s">
+        <v>133</v>
+      </c>
+      <c r="J87">
+        <v>1021003</v>
+      </c>
+      <c r="K87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="H88" t="s">
+        <v>134</v>
+      </c>
+      <c r="I88" t="s">
+        <v>135</v>
+      </c>
+      <c r="J88">
+        <v>1021004</v>
+      </c>
+      <c r="K88" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="16455" windowHeight="7320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="138">
   <si>
     <t>##var</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>经验</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>建筑</t>
   </si>
   <si>
     <t>item_selected_child_type</t>
@@ -1409,7 +1415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1869,152 +1875,152 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="2:11">
-      <c r="B31" t="s">
+    <row r="30" spans="2:11">
+      <c r="H30" t="s">
         <v>66</v>
       </c>
-      <c r="C31" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="I30" t="s">
+        <v>67</v>
+      </c>
+      <c r="J30">
+        <v>9</v>
+      </c>
+      <c r="K30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="2:11">
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
         <v>21</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I32" t="s">
         <v>22</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
-      <c r="B33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
+    <row r="34" spans="2:11">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
         <v>21</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I34" t="s">
         <v>22</v>
       </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="H34" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" t="s">
-        <v>68</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="H35" t="s">
-        <v>69</v>
+        <v>28</v>
+      </c>
+      <c r="I35" t="s">
+        <v>70</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="H37" t="s">
         <v>62</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I37" t="s">
         <v>63</v>
       </c>
-      <c r="J36">
+      <c r="J37">
         <v>3</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K37" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" t="s">
+    <row r="39" spans="2:11">
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
         <v>21</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I39" t="s">
         <v>22</v>
       </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
-      <c r="H39" t="s">
-        <v>71</v>
-      </c>
-      <c r="I39" t="s">
-        <v>72</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41" t="s">
+    <row r="40" spans="2:11">
+      <c r="H40" t="s">
         <v>73</v>
       </c>
-      <c r="C41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="I40" t="s">
         <v>74</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" t="s">
         <v>75</v>
       </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
       <c r="H42" t="s">
         <v>76</v>
       </c>
@@ -2022,7 +2028,7 @@
         <v>77</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="s">
         <v>77</v>
@@ -2036,47 +2042,47 @@
         <v>79</v>
       </c>
       <c r="J43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
-      <c r="B45" t="s">
+    <row r="44" spans="2:11">
+      <c r="H44" t="s">
         <v>80</v>
       </c>
-      <c r="C45" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="I44" t="s">
+        <v>81</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="B46" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
         <v>21</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I46" t="s">
         <v>22</v>
       </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45" t="s">
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="H46" t="s">
-        <v>81</v>
-      </c>
-      <c r="I46" t="s">
-        <v>82</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-      <c r="K46" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2084,53 +2090,53 @@
         <v>83</v>
       </c>
       <c r="I47" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="2:11">
       <c r="H48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="H49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49">
         <v>3</v>
       </c>
-      <c r="K48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="2:11">
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" t="s">
+      <c r="K49" t="s">
         <v>87</v>
       </c>
-      <c r="I50" t="s">
+    </row>
+    <row r="51" customFormat="1" spans="2:11">
+      <c r="B51" t="s">
         <v>88</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="2:11">
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
       <c r="H51" t="s">
         <v>89</v>
       </c>
@@ -2138,7 +2144,7 @@
         <v>90</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="s">
         <v>90</v>
@@ -2146,197 +2152,197 @@
     </row>
     <row r="52" customFormat="1" spans="2:11">
       <c r="H52" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="2:11">
       <c r="H53" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I53" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="2:11">
       <c r="H54" t="s">
-        <v>91</v>
-      </c>
-      <c r="I54"/>
+        <v>58</v>
+      </c>
+      <c r="I54" t="s">
+        <v>59</v>
+      </c>
       <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="2:11">
+      <c r="H55" t="s">
+        <v>93</v>
+      </c>
+      <c r="I55"/>
+      <c r="J55">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="2:11">
-      <c r="B56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56" t="s">
+    <row r="57" spans="2:11">
+      <c r="B57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
         <v>21</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I57" t="s">
         <v>22</v>
       </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="H57" t="s">
-        <v>93</v>
-      </c>
-      <c r="I57" t="s">
-        <v>94</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="K57" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="58" spans="2:11">
       <c r="H58" t="s">
+        <v>95</v>
+      </c>
+      <c r="I58" t="s">
         <v>96</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58" t="s">
         <v>97</v>
-      </c>
-      <c r="J58">
-        <v>2</v>
-      </c>
-      <c r="K58" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="59" spans="2:11">
       <c r="H59" t="s">
+        <v>98</v>
+      </c>
+      <c r="I59" t="s">
         <v>99</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59" t="s">
         <v>100</v>
-      </c>
-      <c r="J59">
-        <v>3</v>
-      </c>
-      <c r="K59" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="H60" t="s">
+        <v>101</v>
+      </c>
+      <c r="I60" t="s">
         <v>102</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60">
+        <v>3</v>
+      </c>
+      <c r="K60" t="s">
         <v>103</v>
-      </c>
-      <c r="J60">
-        <v>4</v>
-      </c>
-      <c r="K60" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="H61" t="s">
+        <v>104</v>
+      </c>
+      <c r="I61" t="s">
         <v>105</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61">
+        <v>4</v>
+      </c>
+      <c r="K61" t="s">
         <v>106</v>
-      </c>
-      <c r="J61">
-        <v>5</v>
-      </c>
-      <c r="K61" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="H62" t="s">
+        <v>107</v>
+      </c>
+      <c r="I62" t="s">
         <v>108</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62" t="s">
         <v>109</v>
       </c>
-      <c r="J62">
+    </row>
+    <row r="63" spans="2:11">
+      <c r="H63" t="s">
+        <v>110</v>
+      </c>
+      <c r="I63" t="s">
+        <v>111</v>
+      </c>
+      <c r="J63">
         <v>6</v>
       </c>
-      <c r="K62" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="K63" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
         <v>21</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I65" t="s">
         <v>22</v>
       </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64" t="s">
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="H65" t="s">
-        <v>93</v>
-      </c>
-      <c r="I65" t="s">
-        <v>94</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="66" spans="2:11">
       <c r="H66" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="I66" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="2:11">
@@ -2347,7 +2353,7 @@
         <v>115</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K67" t="s">
         <v>115</v>
@@ -2361,121 +2367,121 @@
         <v>117</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="70" customFormat="1" spans="2:11">
-      <c r="B70" t="s">
+    <row r="69" spans="2:11">
+      <c r="H69" t="s">
         <v>118</v>
       </c>
-      <c r="C70" t="b">
-        <v>0</v>
-      </c>
-      <c r="E70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="I69" t="s">
+        <v>119</v>
+      </c>
+      <c r="J69">
+        <v>4</v>
+      </c>
+      <c r="K69" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="2:11">
+      <c r="B71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
         <v>21</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I71" t="s">
         <v>22</v>
       </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70" t="s">
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="71" customFormat="1" spans="2:11">
-      <c r="H71" t="s">
-        <v>93</v>
-      </c>
-      <c r="I71" t="s">
-        <v>94</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" t="s">
-        <v>119</v>
-      </c>
-      <c r="C73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="s">
+    <row r="72" customFormat="1" spans="2:11">
+      <c r="H72" t="s">
+        <v>95</v>
+      </c>
+      <c r="I72" t="s">
+        <v>96</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
         <v>21</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I74" t="s">
         <v>22</v>
       </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73" t="s">
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="75" customFormat="1" spans="2:11">
-      <c r="B75" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" t="s">
+    <row r="76" customFormat="1" spans="2:11">
+      <c r="B76" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
         <v>21</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I76" t="s">
         <v>22</v>
       </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="76" customFormat="1" spans="2:11">
-      <c r="H76" t="s">
-        <v>93</v>
-      </c>
-      <c r="I76" t="s">
-        <v>94</v>
-      </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="K76" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
+    <row r="77" customFormat="1" spans="2:11">
       <c r="H77" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="I77" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="2:11">
@@ -2486,7 +2492,7 @@
         <v>115</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" t="s">
         <v>115</v>
@@ -2500,47 +2506,47 @@
         <v>117</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K79" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="81" customFormat="1" spans="2:11">
-      <c r="B81" t="s">
-        <v>121</v>
-      </c>
-      <c r="C81" t="b">
-        <v>0</v>
-      </c>
-      <c r="E81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" t="s">
+    <row r="80" spans="2:11">
+      <c r="H80" t="s">
+        <v>118</v>
+      </c>
+      <c r="I80" t="s">
+        <v>119</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+      <c r="K80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="2:11">
+      <c r="B82" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
         <v>21</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I82" t="s">
         <v>22</v>
       </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81" t="s">
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="H82" t="s">
-        <v>122</v>
-      </c>
-      <c r="I82" t="s">
-        <v>123</v>
-      </c>
-      <c r="J82">
-        <v>1001001</v>
-      </c>
-      <c r="K82" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="83" spans="2:11">
@@ -2551,7 +2557,7 @@
         <v>125</v>
       </c>
       <c r="J83">
-        <v>1001002</v>
+        <v>1001001</v>
       </c>
       <c r="K83" t="s">
         <v>125</v>
@@ -2565,7 +2571,7 @@
         <v>127</v>
       </c>
       <c r="J84">
-        <v>1001003</v>
+        <v>1001002</v>
       </c>
       <c r="K84" t="s">
         <v>127</v>
@@ -2579,7 +2585,7 @@
         <v>129</v>
       </c>
       <c r="J85">
-        <v>1021001</v>
+        <v>1001003</v>
       </c>
       <c r="K85" t="s">
         <v>129</v>
@@ -2593,7 +2599,7 @@
         <v>131</v>
       </c>
       <c r="J86">
-        <v>1021002</v>
+        <v>1021001</v>
       </c>
       <c r="K86" t="s">
         <v>131</v>
@@ -2607,7 +2613,7 @@
         <v>133</v>
       </c>
       <c r="J87">
-        <v>1021003</v>
+        <v>1021002</v>
       </c>
       <c r="K87" t="s">
         <v>133</v>
@@ -2621,10 +2627,24 @@
         <v>135</v>
       </c>
       <c r="J88">
-        <v>1021004</v>
+        <v>1021003</v>
       </c>
       <c r="K88" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="H89" t="s">
+        <v>136</v>
+      </c>
+      <c r="I89" t="s">
+        <v>137</v>
+      </c>
+      <c r="J89">
+        <v>1021004</v>
+      </c>
+      <c r="K89" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="16455" windowHeight="7320"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="138">
   <si>
     <t>##var</t>
   </si>
@@ -1415,7 +1415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -2194,456 +2194,470 @@
     </row>
     <row r="55" customFormat="1" spans="2:11">
       <c r="H55" t="s">
-        <v>93</v>
-      </c>
-      <c r="I55"/>
+        <v>60</v>
+      </c>
+      <c r="I55" t="s">
+        <v>61</v>
+      </c>
       <c r="J55">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" t="s">
+      <c r="K55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="2:11">
+      <c r="H56" t="s">
+        <v>93</v>
+      </c>
+      <c r="I56"/>
+      <c r="J56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" t="s">
         <v>94</v>
       </c>
-      <c r="C57" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
         <v>21</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I58" t="s">
         <v>22</v>
       </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57" t="s">
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="H58" t="s">
-        <v>95</v>
-      </c>
-      <c r="I58" t="s">
-        <v>96</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="59" spans="2:11">
       <c r="H59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I59" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="H60" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I60" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="H61" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="H62" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I62" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="2:11">
       <c r="H63" t="s">
+        <v>107</v>
+      </c>
+      <c r="I63" t="s">
+        <v>108</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="H64" t="s">
         <v>110</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I64" t="s">
         <v>111</v>
       </c>
-      <c r="J63">
+      <c r="J64">
         <v>6</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K64" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="2:11">
-      <c r="B65" t="s">
+    <row r="66" spans="2:11">
+      <c r="B66" t="s">
         <v>113</v>
       </c>
-      <c r="C65" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="C66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
         <v>21</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I66" t="s">
         <v>22</v>
       </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65" t="s">
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="H66" t="s">
-        <v>95</v>
-      </c>
-      <c r="I66" t="s">
-        <v>96</v>
-      </c>
-      <c r="J66">
-        <v>1</v>
-      </c>
-      <c r="K66" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="67" spans="2:11">
       <c r="H67" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="I67" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="2:11">
       <c r="H68" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I68" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="2:11">
       <c r="H69" t="s">
+        <v>116</v>
+      </c>
+      <c r="I69" t="s">
+        <v>117</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
+      </c>
+      <c r="K69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="H70" t="s">
         <v>118</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I70" t="s">
         <v>119</v>
       </c>
-      <c r="J69">
+      <c r="J70">
         <v>4</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K70" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="71" customFormat="1" spans="2:11">
-      <c r="B71" t="s">
+    <row r="72" customFormat="1" spans="2:11">
+      <c r="B72" t="s">
         <v>120</v>
       </c>
-      <c r="C71" t="b">
-        <v>0</v>
-      </c>
-      <c r="E71" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71" t="s">
+      <c r="C72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
         <v>21</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I72" t="s">
         <v>22</v>
       </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71" t="s">
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="72" customFormat="1" spans="2:11">
-      <c r="H72" t="s">
+    <row r="73" customFormat="1" spans="2:11">
+      <c r="H73" t="s">
         <v>95</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I73" t="s">
         <v>96</v>
       </c>
-      <c r="J72">
-        <v>1</v>
-      </c>
-      <c r="K72" t="s">
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="2:11">
-      <c r="B74" t="s">
+    <row r="75" spans="2:11">
+      <c r="B75" t="s">
         <v>121</v>
       </c>
-      <c r="C74" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" t="s">
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
         <v>21</v>
       </c>
-      <c r="I74" t="s">
+      <c r="I75" t="s">
         <v>22</v>
       </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="76" customFormat="1" spans="2:11">
-      <c r="B76" t="s">
+    <row r="77" customFormat="1" spans="2:11">
+      <c r="B77" t="s">
         <v>122</v>
       </c>
-      <c r="C76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
         <v>21</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I77" t="s">
         <v>22</v>
       </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="77" customFormat="1" spans="2:11">
-      <c r="H77" t="s">
+    <row r="78" customFormat="1" spans="2:11">
+      <c r="H78" t="s">
         <v>95</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I78" t="s">
         <v>96</v>
       </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="K77" t="s">
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="H78" t="s">
-        <v>114</v>
-      </c>
-      <c r="I78" t="s">
-        <v>115</v>
-      </c>
-      <c r="J78">
-        <v>2</v>
-      </c>
-      <c r="K78" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="79" spans="2:11">
       <c r="H79" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="2:11">
       <c r="H80" t="s">
+        <v>116</v>
+      </c>
+      <c r="I80" t="s">
+        <v>117</v>
+      </c>
+      <c r="J80">
+        <v>3</v>
+      </c>
+      <c r="K80" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="H81" t="s">
         <v>118</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I81" t="s">
         <v>119</v>
       </c>
-      <c r="J80">
+      <c r="J81">
         <v>4</v>
       </c>
-      <c r="K80" t="s">
+      <c r="K81" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="82" customFormat="1" spans="2:11">
-      <c r="B82" t="s">
+    <row r="83" customFormat="1" spans="2:11">
+      <c r="B83" t="s">
         <v>123</v>
       </c>
-      <c r="C82" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" t="s">
+      <c r="C83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
         <v>21</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I83" t="s">
         <v>22</v>
       </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82" t="s">
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="H83" t="s">
-        <v>124</v>
-      </c>
-      <c r="I83" t="s">
-        <v>125</v>
-      </c>
-      <c r="J83">
-        <v>1001001</v>
-      </c>
-      <c r="K83" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="H84" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I84" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J84">
-        <v>1001002</v>
+        <v>1001001</v>
       </c>
       <c r="K84" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="H85" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I85" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J85">
-        <v>1001003</v>
+        <v>1001002</v>
       </c>
       <c r="K85" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="2:11">
       <c r="H86" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J86">
-        <v>1021001</v>
+        <v>1001003</v>
       </c>
       <c r="K86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="2:11">
       <c r="H87" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I87" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J87">
-        <v>1021002</v>
+        <v>1021001</v>
       </c>
       <c r="K87" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="H88" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I88" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J88">
-        <v>1021003</v>
+        <v>1021002</v>
       </c>
       <c r="K88" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="H89" t="s">
+        <v>134</v>
+      </c>
+      <c r="I89" t="s">
+        <v>135</v>
+      </c>
+      <c r="J89">
+        <v>1021003</v>
+      </c>
+      <c r="K89" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="H90" t="s">
         <v>136</v>
       </c>
-      <c r="I89" t="s">
+      <c r="I90" t="s">
         <v>137</v>
       </c>
-      <c r="J89">
+      <c r="J90">
         <v>1021004</v>
       </c>
-      <c r="K89" t="s">
+      <c r="K90" t="s">
         <v>137</v>
       </c>
     </row>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>建筑</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>资源</t>
   </si>
   <si>
     <t>item_selected_child_type</t>
@@ -1415,7 +1421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1889,152 +1895,152 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="2:11">
-      <c r="B32" t="s">
+    <row r="31" spans="2:11">
+      <c r="H31" t="s">
         <v>68</v>
       </c>
-      <c r="C32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I31" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:11">
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
         <v>21</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I33" t="s">
         <v>22</v>
       </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
-      <c r="B34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" t="s">
+    <row r="35" spans="2:11">
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
         <v>21</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I35" t="s">
         <v>22</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="H35" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" t="s">
-        <v>70</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" t="s">
-        <v>71</v>
+        <v>28</v>
+      </c>
+      <c r="I36" t="s">
+        <v>72</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="H37" t="s">
+        <v>73</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="H38" t="s">
         <v>62</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I38" t="s">
         <v>63</v>
       </c>
-      <c r="J37">
+      <c r="J38">
         <v>3</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K38" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" t="s">
+    <row r="40" spans="2:11">
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
         <v>21</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I40" t="s">
         <v>22</v>
       </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39" t="s">
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
-      <c r="H40" t="s">
-        <v>73</v>
-      </c>
-      <c r="I40" t="s">
-        <v>74</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" t="s">
+    <row r="41" spans="2:11">
+      <c r="H41" t="s">
         <v>75</v>
       </c>
-      <c r="C42" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="s">
+      <c r="I41" t="s">
         <v>76</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" t="s">
         <v>77</v>
       </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
       <c r="H43" t="s">
         <v>78</v>
       </c>
@@ -2042,7 +2048,7 @@
         <v>79</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="s">
         <v>79</v>
@@ -2056,47 +2062,47 @@
         <v>81</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="2:11">
-      <c r="B46" t="s">
+    <row r="45" spans="2:11">
+      <c r="H45" t="s">
         <v>82</v>
       </c>
-      <c r="C46" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="I45" t="s">
+        <v>83</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
         <v>21</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I47" t="s">
         <v>22</v>
       </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46" t="s">
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
-      <c r="H47" t="s">
-        <v>83</v>
-      </c>
-      <c r="I47" t="s">
-        <v>84</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
-      <c r="K47" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -2104,53 +2110,53 @@
         <v>85</v>
       </c>
       <c r="I48" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="2:11">
       <c r="H49" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="H50" t="s">
+        <v>88</v>
+      </c>
+      <c r="I50" t="s">
+        <v>89</v>
+      </c>
+      <c r="J50">
         <v>3</v>
       </c>
-      <c r="K49" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="2:11">
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="K50" t="s">
         <v>89</v>
       </c>
-      <c r="I51" t="s">
+    </row>
+    <row r="52" customFormat="1" spans="2:11">
+      <c r="B52" t="s">
         <v>90</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="2:11">
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
       <c r="H52" t="s">
         <v>91</v>
       </c>
@@ -2158,7 +2164,7 @@
         <v>92</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="s">
         <v>92</v>
@@ -2166,211 +2172,211 @@
     </row>
     <row r="53" customFormat="1" spans="2:11">
       <c r="H53" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="I53" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="2:11">
       <c r="H54" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="2:11">
       <c r="H55" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="2:11">
       <c r="H56" t="s">
-        <v>93</v>
-      </c>
-      <c r="I56"/>
+        <v>60</v>
+      </c>
+      <c r="I56" t="s">
+        <v>61</v>
+      </c>
       <c r="J56">
+        <v>4</v>
+      </c>
+      <c r="K56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="2:11">
+      <c r="H57" t="s">
+        <v>95</v>
+      </c>
+      <c r="I57"/>
+      <c r="J57">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="2:11">
-      <c r="B58" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" t="s">
+    <row r="59" spans="2:11">
+      <c r="B59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
         <v>21</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I59" t="s">
         <v>22</v>
       </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58" t="s">
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="H59" t="s">
-        <v>95</v>
-      </c>
-      <c r="I59" t="s">
-        <v>96</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="H60" t="s">
+        <v>97</v>
+      </c>
+      <c r="I60" t="s">
         <v>98</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
         <v>99</v>
-      </c>
-      <c r="J60">
-        <v>2</v>
-      </c>
-      <c r="K60" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="H61" t="s">
+        <v>100</v>
+      </c>
+      <c r="I61" t="s">
         <v>101</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
         <v>102</v>
-      </c>
-      <c r="J61">
-        <v>3</v>
-      </c>
-      <c r="K61" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="H62" t="s">
+        <v>103</v>
+      </c>
+      <c r="I62" t="s">
         <v>104</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62" t="s">
         <v>105</v>
-      </c>
-      <c r="J62">
-        <v>4</v>
-      </c>
-      <c r="K62" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="63" spans="2:11">
       <c r="H63" t="s">
+        <v>106</v>
+      </c>
+      <c r="I63" t="s">
         <v>107</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63">
+        <v>4</v>
+      </c>
+      <c r="K63" t="s">
         <v>108</v>
-      </c>
-      <c r="J63">
-        <v>5</v>
-      </c>
-      <c r="K63" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="64" spans="2:11">
       <c r="H64" t="s">
+        <v>109</v>
+      </c>
+      <c r="I64" t="s">
         <v>110</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64" t="s">
         <v>111</v>
       </c>
-      <c r="J64">
+    </row>
+    <row r="65" spans="2:11">
+      <c r="H65" t="s">
+        <v>112</v>
+      </c>
+      <c r="I65" t="s">
+        <v>113</v>
+      </c>
+      <c r="J65">
         <v>6</v>
       </c>
-      <c r="K64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" t="s">
-        <v>113</v>
-      </c>
-      <c r="C66" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="K65" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
         <v>21</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I67" t="s">
         <v>22</v>
       </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66" t="s">
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="H67" t="s">
-        <v>95</v>
-      </c>
-      <c r="I67" t="s">
-        <v>96</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="68" spans="2:11">
       <c r="H68" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="I68" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="2:11">
@@ -2381,7 +2387,7 @@
         <v>117</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69" t="s">
         <v>117</v>
@@ -2395,121 +2401,121 @@
         <v>119</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="72" customFormat="1" spans="2:11">
-      <c r="B72" t="s">
+    <row r="71" spans="2:11">
+      <c r="H71" t="s">
         <v>120</v>
       </c>
-      <c r="C72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
+      <c r="I71" t="s">
+        <v>121</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+      <c r="K71" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="2:11">
+      <c r="B73" t="s">
+        <v>122</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
         <v>21</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I73" t="s">
         <v>22</v>
       </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72" t="s">
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="73" customFormat="1" spans="2:11">
-      <c r="H73" t="s">
-        <v>95</v>
-      </c>
-      <c r="I73" t="s">
-        <v>96</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="K73" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" t="s">
-        <v>121</v>
-      </c>
-      <c r="C75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" t="s">
+    <row r="74" customFormat="1" spans="2:11">
+      <c r="H74" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" t="s">
+        <v>98</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" t="s">
+        <v>123</v>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
         <v>21</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I76" t="s">
         <v>22</v>
       </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="77" customFormat="1" spans="2:11">
-      <c r="B77" t="s">
-        <v>122</v>
-      </c>
-      <c r="C77" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" t="s">
+    <row r="78" customFormat="1" spans="2:11">
+      <c r="B78" t="s">
+        <v>124</v>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
         <v>21</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I78" t="s">
         <v>22</v>
       </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77" t="s">
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="78" customFormat="1" spans="2:11">
-      <c r="H78" t="s">
-        <v>95</v>
-      </c>
-      <c r="I78" t="s">
-        <v>96</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
+    <row r="79" customFormat="1" spans="2:11">
       <c r="H79" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="I79" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="2:11">
@@ -2520,7 +2526,7 @@
         <v>117</v>
       </c>
       <c r="J80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K80" t="s">
         <v>117</v>
@@ -2534,47 +2540,47 @@
         <v>119</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="83" customFormat="1" spans="2:11">
-      <c r="B83" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" t="b">
-        <v>0</v>
-      </c>
-      <c r="E83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" t="s">
+    <row r="82" spans="2:11">
+      <c r="H82" t="s">
+        <v>120</v>
+      </c>
+      <c r="I82" t="s">
+        <v>121</v>
+      </c>
+      <c r="J82">
+        <v>4</v>
+      </c>
+      <c r="K82" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="2:11">
+      <c r="B84" t="s">
+        <v>125</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
         <v>21</v>
       </c>
-      <c r="I83" t="s">
+      <c r="I84" t="s">
         <v>22</v>
       </c>
-      <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="K83" t="s">
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="H84" t="s">
-        <v>124</v>
-      </c>
-      <c r="I84" t="s">
-        <v>125</v>
-      </c>
-      <c r="J84">
-        <v>1001001</v>
-      </c>
-      <c r="K84" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="85" spans="2:11">
@@ -2585,7 +2591,7 @@
         <v>127</v>
       </c>
       <c r="J85">
-        <v>1001002</v>
+        <v>1001001</v>
       </c>
       <c r="K85" t="s">
         <v>127</v>
@@ -2599,7 +2605,7 @@
         <v>129</v>
       </c>
       <c r="J86">
-        <v>1001003</v>
+        <v>1001002</v>
       </c>
       <c r="K86" t="s">
         <v>129</v>
@@ -2613,7 +2619,7 @@
         <v>131</v>
       </c>
       <c r="J87">
-        <v>1021001</v>
+        <v>1001003</v>
       </c>
       <c r="K87" t="s">
         <v>131</v>
@@ -2627,7 +2633,7 @@
         <v>133</v>
       </c>
       <c r="J88">
-        <v>1021002</v>
+        <v>10001001</v>
       </c>
       <c r="K88" t="s">
         <v>133</v>
@@ -2641,7 +2647,7 @@
         <v>135</v>
       </c>
       <c r="J89">
-        <v>1021003</v>
+        <v>10001002</v>
       </c>
       <c r="K89" t="s">
         <v>135</v>
@@ -2655,10 +2661,24 @@
         <v>137</v>
       </c>
       <c r="J90">
-        <v>1021004</v>
+        <v>10001003</v>
       </c>
       <c r="K90" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="H91" t="s">
+        <v>138</v>
+      </c>
+      <c r="I91" t="s">
+        <v>139</v>
+      </c>
+      <c r="J91">
+        <v>10001004</v>
+      </c>
+      <c r="K91" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -1421,7 +1421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1994,690 +1994,704 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
-      <c r="B40" t="s">
+    <row r="39" spans="2:11">
+      <c r="H39" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" t="s">
+        <v>67</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" t="s">
         <v>74</v>
       </c>
-      <c r="C40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
         <v>21</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I41" t="s">
         <v>22</v>
       </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
-      <c r="H41" t="s">
+    <row r="42" spans="2:11">
+      <c r="H42" t="s">
         <v>75</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I42" t="s">
         <v>76</v>
       </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="2:11">
-      <c r="B43" t="s">
+    <row r="44" spans="2:11">
+      <c r="B44" t="s">
         <v>77</v>
       </c>
-      <c r="C43" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
         <v>78</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I44" t="s">
         <v>79</v>
       </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43" t="s">
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="H44" t="s">
-        <v>80</v>
-      </c>
-      <c r="I44" t="s">
-        <v>81</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="45" spans="2:11">
       <c r="H45" t="s">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s">
+        <v>81</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="H46" t="s">
         <v>82</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I46" t="s">
         <v>83</v>
       </c>
-      <c r="J45">
+      <c r="J46">
         <v>2</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K46" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="2:11">
-      <c r="B47" t="s">
+    <row r="48" spans="2:11">
+      <c r="B48" t="s">
         <v>84</v>
       </c>
-      <c r="C47" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="C48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
         <v>21</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I48" t="s">
         <v>22</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="s">
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="H48" t="s">
-        <v>85</v>
-      </c>
-      <c r="I48" t="s">
-        <v>86</v>
-      </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-      <c r="K48" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="49" spans="2:11">
       <c r="H49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="2:11">
       <c r="H50" t="s">
+        <v>87</v>
+      </c>
+      <c r="I50" t="s">
+        <v>76</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="H51" t="s">
         <v>88</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I51" t="s">
         <v>89</v>
       </c>
-      <c r="J50">
+      <c r="J51">
         <v>3</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K51" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="2:11">
-      <c r="B52" t="s">
+    <row r="53" customFormat="1" spans="2:11">
+      <c r="B53" t="s">
         <v>90</v>
       </c>
-      <c r="C52" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
         <v>91</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I53" t="s">
         <v>92</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="2:11">
-      <c r="H53" t="s">
-        <v>93</v>
-      </c>
-      <c r="I53" t="s">
-        <v>94</v>
-      </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="2:11">
       <c r="H54" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="I54" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="2:11">
       <c r="H55" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I55" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="2:11">
       <c r="H56" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I56" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="2:11">
       <c r="H57" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" t="s">
+        <v>61</v>
+      </c>
+      <c r="J57">
+        <v>4</v>
+      </c>
+      <c r="K57" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="2:11">
+      <c r="H58" t="s">
         <v>95</v>
       </c>
-      <c r="I57"/>
-      <c r="J57">
+      <c r="I58"/>
+      <c r="J58">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="2:11">
-      <c r="B59" t="s">
+    <row r="60" spans="2:11">
+      <c r="B60" t="s">
         <v>96</v>
       </c>
-      <c r="C59" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
         <v>21</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I60" t="s">
         <v>22</v>
       </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59" t="s">
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="H60" t="s">
-        <v>97</v>
-      </c>
-      <c r="I60" t="s">
-        <v>98</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="H61" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I61" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="H62" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I62" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="2:11">
       <c r="H63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I63" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="2:11">
       <c r="H64" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I64" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="2:11">
       <c r="H65" t="s">
+        <v>109</v>
+      </c>
+      <c r="I65" t="s">
+        <v>110</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
+      <c r="K65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="H66" t="s">
         <v>112</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I66" t="s">
         <v>113</v>
       </c>
-      <c r="J65">
+      <c r="J66">
         <v>6</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K66" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="2:11">
-      <c r="B67" t="s">
+    <row r="68" spans="2:11">
+      <c r="B68" t="s">
         <v>115</v>
       </c>
-      <c r="C67" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
         <v>21</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I68" t="s">
         <v>22</v>
       </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67" t="s">
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="H68" t="s">
-        <v>97</v>
-      </c>
-      <c r="I68" t="s">
-        <v>98</v>
-      </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="K68" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="69" spans="2:11">
       <c r="H69" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="I69" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="J69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="2:11">
       <c r="H70" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="2:11">
       <c r="H71" t="s">
+        <v>118</v>
+      </c>
+      <c r="I71" t="s">
+        <v>119</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="H72" t="s">
         <v>120</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I72" t="s">
         <v>121</v>
       </c>
-      <c r="J71">
+      <c r="J72">
         <v>4</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K72" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="73" customFormat="1" spans="2:11">
-      <c r="B73" t="s">
+    <row r="74" customFormat="1" spans="2:11">
+      <c r="B74" t="s">
         <v>122</v>
       </c>
-      <c r="C73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="s">
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
         <v>21</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I74" t="s">
         <v>22</v>
       </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73" t="s">
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="74" customFormat="1" spans="2:11">
-      <c r="H74" t="s">
+    <row r="75" customFormat="1" spans="2:11">
+      <c r="H75" t="s">
         <v>97</v>
       </c>
-      <c r="I74" t="s">
+      <c r="I75" t="s">
         <v>98</v>
       </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="2:11">
-      <c r="B76" t="s">
+    <row r="77" spans="2:11">
+      <c r="B77" t="s">
         <v>123</v>
       </c>
-      <c r="C76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
         <v>21</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I77" t="s">
         <v>22</v>
       </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="78" customFormat="1" spans="2:11">
-      <c r="B78" t="s">
+    <row r="79" customFormat="1" spans="2:11">
+      <c r="B79" t="s">
         <v>124</v>
       </c>
-      <c r="C78" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
         <v>21</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I79" t="s">
         <v>22</v>
       </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78" t="s">
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="79" customFormat="1" spans="2:11">
-      <c r="H79" t="s">
+    <row r="80" customFormat="1" spans="2:11">
+      <c r="H80" t="s">
         <v>97</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I80" t="s">
         <v>98</v>
       </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="K79" t="s">
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="H80" t="s">
-        <v>116</v>
-      </c>
-      <c r="I80" t="s">
-        <v>117</v>
-      </c>
-      <c r="J80">
-        <v>2</v>
-      </c>
-      <c r="K80" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="81" spans="2:11">
       <c r="H81" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="2:11">
       <c r="H82" t="s">
+        <v>118</v>
+      </c>
+      <c r="I82" t="s">
+        <v>119</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+      <c r="K82" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="H83" t="s">
         <v>120</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I83" t="s">
         <v>121</v>
       </c>
-      <c r="J82">
+      <c r="J83">
         <v>4</v>
       </c>
-      <c r="K82" t="s">
+      <c r="K83" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="84" customFormat="1" spans="2:11">
-      <c r="B84" t="s">
+    <row r="85" customFormat="1" spans="2:11">
+      <c r="B85" t="s">
         <v>125</v>
       </c>
-      <c r="C84" t="b">
-        <v>0</v>
-      </c>
-      <c r="E84" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" t="s">
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
         <v>21</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I85" t="s">
         <v>22</v>
       </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84" t="s">
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="H85" t="s">
-        <v>126</v>
-      </c>
-      <c r="I85" t="s">
-        <v>127</v>
-      </c>
-      <c r="J85">
-        <v>1001001</v>
-      </c>
-      <c r="K85" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="86" spans="2:11">
       <c r="H86" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I86" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J86">
-        <v>1001002</v>
+        <v>1001001</v>
       </c>
       <c r="K86" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" spans="2:11">
       <c r="H87" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I87" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J87">
-        <v>1001003</v>
+        <v>1001002</v>
       </c>
       <c r="K87" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="H88" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I88" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J88">
-        <v>10001001</v>
+        <v>1001003</v>
       </c>
       <c r="K88" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="H89" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I89" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J89">
-        <v>10001002</v>
+        <v>10001001</v>
       </c>
       <c r="K89" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="2:11">
       <c r="H90" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I90" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J90">
-        <v>10001003</v>
+        <v>10001002</v>
       </c>
       <c r="K90" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="H91" t="s">
+        <v>136</v>
+      </c>
+      <c r="I91" t="s">
+        <v>137</v>
+      </c>
+      <c r="J91">
+        <v>10001003</v>
+      </c>
+      <c r="K91" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="H92" t="s">
         <v>138</v>
       </c>
-      <c r="I91" t="s">
+      <c r="I92" t="s">
         <v>139</v>
       </c>
-      <c r="J91">
+      <c r="J92">
         <v>10001004</v>
       </c>
-      <c r="K91" t="s">
+      <c r="K92" t="s">
         <v>139</v>
       </c>
     </row>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="151">
   <si>
     <t>##var</t>
   </si>
@@ -393,6 +393,39 @@
   </si>
   <si>
     <t>名臣</t>
+  </si>
+  <si>
+    <t>building_type</t>
+  </si>
+  <si>
+    <t>farmland</t>
+  </si>
+  <si>
+    <t>农田</t>
+  </si>
+  <si>
+    <t>lumber_mill</t>
+  </si>
+  <si>
+    <t>伐木场</t>
+  </si>
+  <si>
+    <t>quarry</t>
+  </si>
+  <si>
+    <t>采石场</t>
+  </si>
+  <si>
+    <t>mine</t>
+  </si>
+  <si>
+    <t>矿场</t>
+  </si>
+  <si>
+    <t>folk_house</t>
+  </si>
+  <si>
+    <t>民居</t>
   </si>
   <si>
     <t>frame_type</t>
@@ -1421,7 +1454,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -2460,239 +2493,333 @@
     </row>
     <row r="75" customFormat="1" spans="2:11">
       <c r="H75" t="s">
+        <v>123</v>
+      </c>
+      <c r="I75" t="s">
+        <v>124</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="2:11">
+      <c r="H76" t="s">
+        <v>125</v>
+      </c>
+      <c r="I76" t="s">
+        <v>126</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" spans="2:11">
+      <c r="H77" t="s">
+        <v>127</v>
+      </c>
+      <c r="I77" t="s">
+        <v>128</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" spans="2:11">
+      <c r="H78" t="s">
+        <v>129</v>
+      </c>
+      <c r="I78" t="s">
+        <v>130</v>
+      </c>
+      <c r="J78">
+        <v>4</v>
+      </c>
+      <c r="K78" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="2:11">
+      <c r="H79" t="s">
+        <v>131</v>
+      </c>
+      <c r="I79" t="s">
+        <v>132</v>
+      </c>
+      <c r="J79">
+        <v>5</v>
+      </c>
+      <c r="K79" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1"/>
+    <row r="81" customFormat="1" spans="2:11">
+      <c r="B81" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="2:11">
+      <c r="H82" t="s">
         <v>97</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I82" t="s">
         <v>98</v>
       </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="2:11">
-      <c r="B77" t="s">
-        <v>123</v>
-      </c>
-      <c r="C77" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" t="s">
+    <row r="84" spans="2:11">
+      <c r="B84" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
         <v>21</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I84" t="s">
         <v>22</v>
       </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77" t="s">
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="79" customFormat="1" spans="2:11">
-      <c r="B79" t="s">
-        <v>124</v>
-      </c>
-      <c r="C79" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79" t="s">
+    <row r="86" customFormat="1" spans="2:11">
+      <c r="B86" t="s">
+        <v>135</v>
+      </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
         <v>21</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I86" t="s">
         <v>22</v>
       </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79" t="s">
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="80" customFormat="1" spans="2:11">
-      <c r="H80" t="s">
+    <row r="87" customFormat="1" spans="2:11">
+      <c r="H87" t="s">
         <v>97</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I87" t="s">
         <v>98</v>
       </c>
-      <c r="J80">
-        <v>1</v>
-      </c>
-      <c r="K80" t="s">
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="H81" t="s">
-        <v>116</v>
-      </c>
-      <c r="I81" t="s">
-        <v>117</v>
-      </c>
-      <c r="J81">
-        <v>2</v>
-      </c>
-      <c r="K81" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="H82" t="s">
-        <v>118</v>
-      </c>
-      <c r="I82" t="s">
-        <v>119</v>
-      </c>
-      <c r="J82">
-        <v>3</v>
-      </c>
-      <c r="K82" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="H83" t="s">
-        <v>120</v>
-      </c>
-      <c r="I83" t="s">
-        <v>121</v>
-      </c>
-      <c r="J83">
-        <v>4</v>
-      </c>
-      <c r="K83" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" spans="2:11">
-      <c r="B85" t="s">
-        <v>125</v>
-      </c>
-      <c r="C85" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" t="s">
-        <v>21</v>
-      </c>
-      <c r="I85" t="s">
-        <v>22</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="H86" t="s">
-        <v>126</v>
-      </c>
-      <c r="I86" t="s">
-        <v>127</v>
-      </c>
-      <c r="J86">
-        <v>1001001</v>
-      </c>
-      <c r="K86" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="H87" t="s">
-        <v>128</v>
-      </c>
-      <c r="I87" t="s">
-        <v>129</v>
-      </c>
-      <c r="J87">
-        <v>1001002</v>
-      </c>
-      <c r="K87" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="H88" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I88" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="J88">
-        <v>1001003</v>
+        <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="H89" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I89" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="J89">
-        <v>10001001</v>
+        <v>3</v>
       </c>
       <c r="K89" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="2:11">
       <c r="H90" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="I90" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="J90">
+        <v>4</v>
+      </c>
+      <c r="K90" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="2:11">
+      <c r="B92" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s">
+        <v>22</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="H93" t="s">
+        <v>137</v>
+      </c>
+      <c r="I93" t="s">
+        <v>138</v>
+      </c>
+      <c r="J93">
+        <v>1001001</v>
+      </c>
+      <c r="K93" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="H94" t="s">
+        <v>139</v>
+      </c>
+      <c r="I94" t="s">
+        <v>140</v>
+      </c>
+      <c r="J94">
+        <v>1001002</v>
+      </c>
+      <c r="K94" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="H95" t="s">
+        <v>141</v>
+      </c>
+      <c r="I95" t="s">
+        <v>142</v>
+      </c>
+      <c r="J95">
+        <v>1001003</v>
+      </c>
+      <c r="K95" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="H96" t="s">
+        <v>143</v>
+      </c>
+      <c r="I96" t="s">
+        <v>144</v>
+      </c>
+      <c r="J96">
+        <v>10001001</v>
+      </c>
+      <c r="K96" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97" spans="8:11">
+      <c r="H97" t="s">
+        <v>145</v>
+      </c>
+      <c r="I97" t="s">
+        <v>146</v>
+      </c>
+      <c r="J97">
         <v>10001002</v>
       </c>
-      <c r="K90" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="H91" t="s">
-        <v>136</v>
-      </c>
-      <c r="I91" t="s">
-        <v>137</v>
-      </c>
-      <c r="J91">
+      <c r="K97" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="98" spans="8:11">
+      <c r="H98" t="s">
+        <v>147</v>
+      </c>
+      <c r="I98" t="s">
+        <v>148</v>
+      </c>
+      <c r="J98">
         <v>10001003</v>
       </c>
-      <c r="K91" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="H92" t="s">
-        <v>138</v>
-      </c>
-      <c r="I92" t="s">
-        <v>139</v>
-      </c>
-      <c r="J92">
+      <c r="K98" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="99" spans="8:11">
+      <c r="H99" t="s">
+        <v>149</v>
+      </c>
+      <c r="I99" t="s">
+        <v>150</v>
+      </c>
+      <c r="J99">
         <v>10001004</v>
       </c>
-      <c r="K92" t="s">
-        <v>139</v>
+      <c r="K99" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/enums.xlsx
+++ b/data/config/luban/config/enums.xlsx
@@ -2561,7 +2561,6 @@
         <v>132</v>
       </c>
     </row>
-    <row r="80" customFormat="1"/>
     <row r="81" customFormat="1" spans="2:11">
       <c r="B81" t="s">
         <v>133</v>
